--- a/artfynd/A 8221-2026 artfynd.xlsx
+++ b/artfynd/A 8221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130081457</v>
+        <v>133646355</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787728</v>
+        <v>787515</v>
       </c>
       <c r="R2" t="n">
-        <v>7248228</v>
+        <v>7248394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>06:01</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06:01</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -789,6 +769,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133645766</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>787515</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7248237</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130081457</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>787728</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7248228</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8221-2026 artfynd.xlsx
+++ b/artfynd/A 8221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646355</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>